--- a/backend/src/OrderMgmt.WebApi/templates/template_baogia.xlsx
+++ b/backend/src/OrderMgmt.WebApi/templates/template_baogia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Hà nội, ngày 28 tháng 05 năm 2026</t>
   </si>
@@ -45,10 +45,6 @@
   </si>
   <si>
     <t>2.</t>
-  </si>
-  <si>
-    <t>Xốp tấm EPS, màu trắng, KT:1000*2000*100mm
-- Tỷ trọng 6kg/khối</t>
   </si>
   <si>
     <t>STT</t>
@@ -356,6 +352,18 @@
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -374,9 +382,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -388,15 +393,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1915,108 +1911,108 @@
   <sheetData>
     <row r="6" spans="1:6" ht="0.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
-        <v>25</v>
+      <c r="A7" s="19" t="s">
+        <v>24</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
-        <v>24</v>
+      <c r="A8" s="20" t="s">
+        <v>23</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:6" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
     </row>
     <row r="12" spans="1:6" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>1</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="12">
         <v>20</v>
@@ -2028,15 +2024,15 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>2</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="13">
@@ -2049,7 +2045,7 @@
     <row r="17" spans="1:15803" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="10">
         <f>SUM(C15:C16)</f>
@@ -2065,7 +2061,7 @@
     <row r="18" spans="1:15803" s="2" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="16"/>
@@ -2079,7 +2075,7 @@
     <row r="19" spans="1:15803" s="2" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="16"/>
@@ -2091,7 +2087,7 @@
     <row r="20" spans="1:15803" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="16"/>
@@ -17899,10 +17895,10 @@
     </row>
     <row r="21" spans="1:15803" s="2" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
-      <c r="B21" s="28" t="s">
-        <v>16</v>
+      <c r="B21" s="31" t="s">
+        <v>15</v>
       </c>
-      <c r="C21" s="29"/>
+      <c r="C21" s="32"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17">
@@ -33707,75 +33703,70 @@
       <c r="WIU21" s="1"/>
     </row>
     <row r="22" spans="1:15803" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="27"/>
+    </row>
+    <row r="23" spans="1:15803" x14ac:dyDescent="0.3">
+      <c r="B23" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="23"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
     </row>
-    <row r="23" spans="1:15803" x14ac:dyDescent="0.3">
-      <c r="B23" s="22" t="s">
+    <row r="24" spans="1:15803" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="B24" s="27"/>
     </row>
-    <row r="24" spans="1:15803" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23" t="s">
+    <row r="25" spans="1:15803" x14ac:dyDescent="0.3">
+      <c r="B25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="23"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
     </row>
-    <row r="25" spans="1:15803" x14ac:dyDescent="0.3">
-      <c r="B25" s="22" t="s">
+    <row r="26" spans="1:15803" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
+      <c r="B26" s="27"/>
     </row>
-    <row r="26" spans="1:15803" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="23" t="s">
+    <row r="27" spans="1:15803" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="23"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
     </row>
-    <row r="27" spans="1:15803" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="24" t="s">
+    <row r="28" spans="1:15803" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-    </row>
-    <row r="28" spans="1:15803" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
     </row>
     <row r="29" spans="1:15803" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="D29" s="20" t="s">
-        <v>31</v>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="D29" s="24" t="s">
+        <v>30</v>
       </c>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B28:F28"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="A9:F9"/>
@@ -33788,6 +33779,11 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B28:F28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.25" top="0.5" bottom="0.75" header="0.05" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
